--- a/reference/2026-07-15-ec225-level-flight-data-2A1b.xlsx
+++ b/reference/2026-07-15-ec225-level-flight-data-2A1b.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregoryhock/Library/Mobile Documents/com~apple~CloudDocs/ACHI/EC225-tools/Level Flight Performance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregoryhock/Library/Mobile Documents/com~apple~CloudDocs/ACHI/EC225-tools/ec225-cruise-torque/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F142F8-2867-D94D-AF68-E589A9DA8374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D7ED49-ED8B-A843-B2F3-E415E17217A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29440" windowHeight="17940" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29440" windowHeight="17900" firstSheet="20" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -710,6 +710,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -727,15 +736,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1418,7 +1418,7 @@
       </c>
     </row>
     <row r="48" spans="2:5" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="37" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1450,43 +1450,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -1869,67 +1869,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -1966,10 +1966,10 @@
       <c r="M17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="38" t="s">
+      <c r="O17" s="30" t="s">
         <v>55</v>
       </c>
       <c r="P17" s="10"/>
@@ -2425,27 +2425,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -2458,6 +2458,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -2465,13 +2472,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2487,43 +2487,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -2906,69 +2906,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -3484,27 +3484,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -3517,6 +3517,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -3524,13 +3531,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3547,43 +3547,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -3964,67 +3964,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -4516,27 +4516,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -4549,6 +4549,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -4556,13 +4563,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4579,43 +4579,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -4998,65 +4998,65 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -5492,27 +5492,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -5525,6 +5525,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -5532,13 +5539,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5944,67 +5944,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -6484,27 +6484,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -6934,67 +6934,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -7486,27 +7486,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -7546,43 +7546,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -7965,67 +7965,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -8521,27 +8521,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -8554,6 +8554,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -8561,13 +8568,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8584,43 +8584,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -9003,69 +9003,69 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="32"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -9569,27 +9569,27 @@
       <c r="U26" s="9"/>
     </row>
     <row r="28" spans="1:21" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -9602,6 +9602,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="J16:K16"/>
@@ -9611,12 +9617,6 @@
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9633,43 +9633,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -10052,67 +10052,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -10576,27 +10576,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -10609,6 +10609,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -10616,13 +10623,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11029,67 +11029,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -11581,27 +11581,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -12031,63 +12031,63 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -12523,27 +12523,27 @@
       <c r="Q26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -12972,69 +12972,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -13538,27 +13538,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -13599,43 +13599,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -14018,69 +14018,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -14576,27 +14576,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -14609,6 +14609,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -14616,13 +14623,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -14639,43 +14639,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -15058,67 +15058,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -15578,27 +15578,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -15611,6 +15611,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -15618,13 +15625,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15641,43 +15641,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -15950,54 +15950,76 @@
         <v>10000</v>
       </c>
       <c r="B11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="L11" s="13">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>10500</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="B12" s="13">
+        <v>115</v>
+      </c>
+      <c r="C12" s="13">
+        <v>115</v>
+      </c>
+      <c r="D12" s="13">
+        <v>115</v>
+      </c>
+      <c r="E12" s="13">
+        <v>115</v>
+      </c>
+      <c r="F12" s="13">
+        <v>115</v>
+      </c>
+      <c r="G12" s="13">
+        <v>115</v>
+      </c>
+      <c r="H12" s="13">
+        <v>115</v>
+      </c>
+      <c r="I12" s="13">
+        <v>115</v>
+      </c>
+      <c r="J12" s="13">
+        <v>115</v>
+      </c>
+      <c r="K12" s="13">
+        <v>115</v>
+      </c>
+      <c r="L12" s="13">
+        <v>115</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
@@ -16016,67 +16038,67 @@
       <c r="L13" s="13"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -16508,27 +16530,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -16541,6 +16563,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -16548,13 +16577,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -16960,69 +16982,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -17522,27 +17544,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -17972,69 +17994,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -18514,27 +18536,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -18575,43 +18597,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -18921,17 +18943,39 @@
       <c r="A12" s="8">
         <v>10500</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="B12" s="13">
+        <v>115</v>
+      </c>
+      <c r="C12" s="13">
+        <v>115</v>
+      </c>
+      <c r="D12" s="13">
+        <v>115</v>
+      </c>
+      <c r="E12" s="13">
+        <v>115</v>
+      </c>
+      <c r="F12" s="13">
+        <v>115</v>
+      </c>
+      <c r="G12" s="13">
+        <v>115</v>
+      </c>
+      <c r="H12" s="13">
+        <v>115</v>
+      </c>
+      <c r="I12" s="13">
+        <v>115</v>
+      </c>
+      <c r="J12" s="13">
+        <v>115</v>
+      </c>
+      <c r="K12" s="13">
+        <v>115</v>
+      </c>
+      <c r="L12" s="13">
+        <v>115</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
@@ -18950,67 +18994,67 @@
       <c r="L13" s="13"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -19462,27 +19506,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -19495,6 +19539,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -19502,13 +19553,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -19525,43 +19569,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -19829,17 +19873,39 @@
       <c r="A11" s="8">
         <v>10000</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+      <c r="B11" s="13">
+        <v>115</v>
+      </c>
+      <c r="C11" s="13">
+        <v>115</v>
+      </c>
+      <c r="D11" s="13">
+        <v>115</v>
+      </c>
+      <c r="E11" s="13">
+        <v>115</v>
+      </c>
+      <c r="F11" s="13">
+        <v>115</v>
+      </c>
+      <c r="G11" s="13">
+        <v>115</v>
+      </c>
+      <c r="H11" s="13">
+        <v>115</v>
+      </c>
+      <c r="I11" s="13">
+        <v>115</v>
+      </c>
+      <c r="J11" s="13">
+        <v>115</v>
+      </c>
+      <c r="K11" s="13">
+        <v>115</v>
+      </c>
+      <c r="L11" s="13">
+        <v>115</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
@@ -19874,67 +19940,67 @@
       <c r="L13" s="13"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -20350,27 +20416,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -20383,6 +20449,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -20390,13 +20463,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -20413,43 +20479,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -20645,17 +20711,39 @@
       <c r="A9" s="8">
         <v>9000</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="B9" s="13">
+        <v>112</v>
+      </c>
+      <c r="C9" s="13">
+        <v>112</v>
+      </c>
+      <c r="D9" s="13">
+        <v>112</v>
+      </c>
+      <c r="E9" s="13">
+        <v>112</v>
+      </c>
+      <c r="F9" s="13">
+        <v>112</v>
+      </c>
+      <c r="G9" s="13">
+        <v>112</v>
+      </c>
+      <c r="H9" s="13">
+        <v>112</v>
+      </c>
+      <c r="I9" s="13">
+        <v>112</v>
+      </c>
+      <c r="J9" s="13">
+        <v>112</v>
+      </c>
+      <c r="K9" s="13">
+        <v>112</v>
+      </c>
+      <c r="L9" s="13">
+        <v>112</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
@@ -20722,65 +20810,65 @@
       <c r="L13" s="13"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -21148,27 +21236,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -21181,6 +21269,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -21188,13 +21283,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21600,67 +21688,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -22148,27 +22236,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -22209,43 +22297,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -22628,67 +22716,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -22776,7 +22864,7 @@
       <c r="M18" s="13">
         <v>678</v>
       </c>
-      <c r="N18" s="36">
+      <c r="N18" s="28">
         <v>86</v>
       </c>
       <c r="O18" s="13">
@@ -23184,27 +23272,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -23217,6 +23305,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -23224,13 +23319,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23247,43 +23335,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -23666,67 +23754,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -24226,27 +24314,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -24259,6 +24347,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -24266,13 +24361,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24288,43 +24376,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -24707,69 +24795,69 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -25293,27 +25381,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -25326,6 +25414,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -25333,13 +25428,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25356,43 +25444,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -25775,67 +25863,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -26323,27 +26411,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -26356,6 +26444,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="F16:G16"/>
@@ -26363,13 +26458,6 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26774,67 +26862,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -27334,27 +27422,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -27784,67 +27872,67 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="32"/>
+      <c r="J16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="32"/>
+      <c r="N16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -28328,27 +28416,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>

--- a/reference/2026-07-15-ec225-level-flight-data-2A1b.xlsx
+++ b/reference/2026-07-15-ec225-level-flight-data-2A1b.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregoryhock/Library/Mobile Documents/com~apple~CloudDocs/ACHI/EC225-tools/ec225-cruise-torque/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D7ED49-ED8B-A843-B2F3-E415E17217A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CDEE86-7B78-0E4F-BEB8-2388D4B7E81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29440" windowHeight="17900" firstSheet="20" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="320" yWindow="680" windowWidth="29440" windowHeight="17900" firstSheet="20" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -719,23 +719,23 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1418,7 +1418,7 @@
       </c>
     </row>
     <row r="48" spans="2:5" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="38" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1450,43 +1450,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -1872,64 +1872,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -2425,27 +2425,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -2458,6 +2458,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -2465,13 +2472,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2487,43 +2487,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -2909,66 +2909,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -3484,27 +3484,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -3517,6 +3517,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -3524,13 +3531,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3547,43 +3547,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -3967,64 +3967,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -4516,27 +4516,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -4549,6 +4549,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -4556,13 +4563,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4579,43 +4579,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -5001,62 +5001,62 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -5492,27 +5492,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -5525,6 +5525,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -5532,13 +5539,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5947,64 +5947,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -6484,27 +6484,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -6937,64 +6937,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -7486,27 +7486,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -7546,43 +7546,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -7968,64 +7968,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -8521,27 +8521,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -8554,6 +8554,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -8561,13 +8568,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8584,43 +8584,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -9006,66 +9006,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="36"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -9569,27 +9569,27 @@
       <c r="U26" s="9"/>
     </row>
     <row r="28" spans="1:21" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -9602,12 +9602,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D16:E16"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="A28:S28"/>
     <mergeCell ref="J16:K16"/>
@@ -9617,6 +9611,12 @@
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9633,43 +9633,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -10055,64 +10055,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -10576,27 +10576,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -10609,6 +10609,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -10616,13 +10623,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11032,64 +11032,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -11581,27 +11581,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -12034,60 +12034,60 @@
       <c r="A15" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -12523,27 +12523,27 @@
       <c r="Q26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -12975,66 +12975,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -13538,27 +13538,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -13599,43 +13599,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -14021,66 +14021,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -14576,27 +14576,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -14609,6 +14609,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -14616,13 +14623,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -14639,43 +14639,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -15061,64 +15061,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -15578,27 +15578,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -15611,6 +15611,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -15618,13 +15625,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15641,43 +15641,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -16041,64 +16041,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -16288,8 +16288,12 @@
       <c r="M20" s="13">
         <v>583</v>
       </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="N20" s="13">
+        <v>80</v>
+      </c>
+      <c r="O20" s="13">
+        <v>645</v>
+      </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
@@ -16329,8 +16333,12 @@
       <c r="K21" s="13">
         <v>545</v>
       </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="L21" s="13">
+        <v>74</v>
+      </c>
+      <c r="M21" s="13">
+        <v>607</v>
+      </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -16372,8 +16380,12 @@
       <c r="K22" s="13">
         <v>578</v>
       </c>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="L22" s="13">
+        <v>78</v>
+      </c>
+      <c r="M22" s="13">
+        <v>635</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -16452,8 +16464,12 @@
       <c r="I24" s="13">
         <v>600</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="J24" s="13">
+        <v>80</v>
+      </c>
+      <c r="K24" s="13">
+        <v>645</v>
+      </c>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
@@ -16485,8 +16501,12 @@
       <c r="G25" s="13">
         <v>600</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+      <c r="H25" s="13">
+        <v>80</v>
+      </c>
+      <c r="I25" s="13">
+        <v>645</v>
+      </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
@@ -16514,8 +16534,12 @@
       <c r="E26" s="13">
         <v>618</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
+      <c r="F26" s="13">
+        <v>80</v>
+      </c>
+      <c r="G26" s="13">
+        <v>645</v>
+      </c>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
@@ -16530,27 +16554,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="19"/>
@@ -16563,6 +16587,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -16570,13 +16601,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -16985,66 +17009,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -17544,27 +17568,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -17997,66 +18021,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -18536,27 +18560,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -18597,43 +18621,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -18944,117 +18968,139 @@
         <v>10500</v>
       </c>
       <c r="B12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L12" s="13">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>11000</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="B13" s="13">
+        <v>100</v>
+      </c>
+      <c r="C13" s="13">
+        <v>100</v>
+      </c>
+      <c r="D13" s="13">
+        <v>100</v>
+      </c>
+      <c r="E13" s="13">
+        <v>100</v>
+      </c>
+      <c r="F13" s="13">
+        <v>100</v>
+      </c>
+      <c r="G13" s="13">
+        <v>100</v>
+      </c>
+      <c r="H13" s="13">
+        <v>100</v>
+      </c>
+      <c r="I13" s="13">
+        <v>100</v>
+      </c>
+      <c r="J13" s="13">
+        <v>100</v>
+      </c>
+      <c r="K13" s="13">
+        <v>100</v>
+      </c>
+      <c r="L13" s="13">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -19383,8 +19429,12 @@
       <c r="K23" s="13">
         <v>595</v>
       </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
+      <c r="L23" s="13">
+        <v>87</v>
+      </c>
+      <c r="M23" s="13">
+        <v>670</v>
+      </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -19463,8 +19513,12 @@
       <c r="I25" s="13">
         <v>640</v>
       </c>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="J25" s="13">
+        <v>92</v>
+      </c>
+      <c r="K25" s="13">
+        <v>675</v>
+      </c>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
@@ -19490,10 +19544,18 @@
       <c r="E26" s="13">
         <v>610</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="F26" s="13">
+        <v>84</v>
+      </c>
+      <c r="G26" s="13">
+        <v>650</v>
+      </c>
+      <c r="H26" s="13">
+        <v>90</v>
+      </c>
+      <c r="I26" s="13">
+        <v>665</v>
+      </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
@@ -19506,27 +19568,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -19539,6 +19601,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -19546,13 +19615,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -19569,43 +19631,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -19906,6 +19968,944 @@
       <c r="L11" s="13">
         <v>115</v>
       </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
+        <v>10500</v>
+      </c>
+      <c r="B12" s="13">
+        <v>90</v>
+      </c>
+      <c r="C12" s="13">
+        <v>90</v>
+      </c>
+      <c r="D12" s="13">
+        <v>90</v>
+      </c>
+      <c r="E12" s="13">
+        <v>90</v>
+      </c>
+      <c r="F12" s="13">
+        <v>90</v>
+      </c>
+      <c r="G12" s="13">
+        <v>90</v>
+      </c>
+      <c r="H12" s="13">
+        <v>90</v>
+      </c>
+      <c r="I12" s="13">
+        <v>90</v>
+      </c>
+      <c r="J12" s="13">
+        <v>90</v>
+      </c>
+      <c r="K12" s="13">
+        <v>90</v>
+      </c>
+      <c r="L12" s="13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <v>11000</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="34"/>
+      <c r="B17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
+        <v>7000</v>
+      </c>
+      <c r="B18" s="13">
+        <v>34</v>
+      </c>
+      <c r="C18" s="13">
+        <v>379</v>
+      </c>
+      <c r="D18" s="13">
+        <v>37</v>
+      </c>
+      <c r="E18" s="13">
+        <v>388</v>
+      </c>
+      <c r="F18" s="13">
+        <v>40</v>
+      </c>
+      <c r="G18" s="13">
+        <v>405</v>
+      </c>
+      <c r="H18" s="13">
+        <v>45</v>
+      </c>
+      <c r="I18" s="13">
+        <v>430</v>
+      </c>
+      <c r="J18" s="13">
+        <v>51</v>
+      </c>
+      <c r="K18" s="13">
+        <v>460</v>
+      </c>
+      <c r="L18" s="13">
+        <v>60</v>
+      </c>
+      <c r="M18" s="13">
+        <v>511</v>
+      </c>
+      <c r="N18" s="13">
+        <v>72</v>
+      </c>
+      <c r="O18" s="13">
+        <v>580</v>
+      </c>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B19" s="13">
+        <v>37</v>
+      </c>
+      <c r="C19" s="13">
+        <v>392</v>
+      </c>
+      <c r="D19" s="13">
+        <v>39</v>
+      </c>
+      <c r="E19" s="13">
+        <v>401</v>
+      </c>
+      <c r="F19" s="13">
+        <v>43</v>
+      </c>
+      <c r="G19" s="13">
+        <v>419</v>
+      </c>
+      <c r="H19" s="13">
+        <v>48</v>
+      </c>
+      <c r="I19" s="13">
+        <v>445</v>
+      </c>
+      <c r="J19" s="13">
+        <v>55</v>
+      </c>
+      <c r="K19" s="13">
+        <v>480</v>
+      </c>
+      <c r="L19" s="13">
+        <v>64</v>
+      </c>
+      <c r="M19" s="13">
+        <v>532</v>
+      </c>
+      <c r="N19" s="13">
+        <v>76</v>
+      </c>
+      <c r="O19" s="13">
+        <v>605</v>
+      </c>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
+        <v>8000</v>
+      </c>
+      <c r="B20" s="13">
+        <v>40</v>
+      </c>
+      <c r="C20" s="13">
+        <v>407</v>
+      </c>
+      <c r="D20" s="13">
+        <v>42</v>
+      </c>
+      <c r="E20" s="13">
+        <v>418</v>
+      </c>
+      <c r="F20" s="13">
+        <v>46</v>
+      </c>
+      <c r="G20" s="13">
+        <v>436</v>
+      </c>
+      <c r="H20" s="13">
+        <v>52</v>
+      </c>
+      <c r="I20" s="13">
+        <v>461</v>
+      </c>
+      <c r="J20" s="13">
+        <v>59</v>
+      </c>
+      <c r="K20" s="13">
+        <v>502</v>
+      </c>
+      <c r="L20" s="13">
+        <v>69</v>
+      </c>
+      <c r="M20" s="13">
+        <v>562</v>
+      </c>
+      <c r="N20" s="13">
+        <v>80</v>
+      </c>
+      <c r="O20" s="13">
+        <v>630</v>
+      </c>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <v>8500</v>
+      </c>
+      <c r="B21" s="13">
+        <v>44</v>
+      </c>
+      <c r="C21" s="13">
+        <v>425</v>
+      </c>
+      <c r="D21" s="13">
+        <v>46</v>
+      </c>
+      <c r="E21" s="13">
+        <v>437</v>
+      </c>
+      <c r="F21" s="13">
+        <v>50</v>
+      </c>
+      <c r="G21" s="13">
+        <v>456</v>
+      </c>
+      <c r="H21" s="13">
+        <v>56</v>
+      </c>
+      <c r="I21" s="13">
+        <v>486</v>
+      </c>
+      <c r="J21" s="13">
+        <v>64</v>
+      </c>
+      <c r="K21" s="13">
+        <v>532</v>
+      </c>
+      <c r="L21" s="13">
+        <v>75</v>
+      </c>
+      <c r="M21" s="13">
+        <v>602</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>9000</v>
+      </c>
+      <c r="B22" s="13">
+        <v>48</v>
+      </c>
+      <c r="C22" s="13">
+        <v>448</v>
+      </c>
+      <c r="D22" s="13">
+        <v>51</v>
+      </c>
+      <c r="E22" s="13">
+        <v>460</v>
+      </c>
+      <c r="F22" s="13">
+        <v>55</v>
+      </c>
+      <c r="G22" s="13">
+        <v>481</v>
+      </c>
+      <c r="H22" s="13">
+        <v>62</v>
+      </c>
+      <c r="I22" s="13">
+        <v>520</v>
+      </c>
+      <c r="J22" s="13">
+        <v>71</v>
+      </c>
+      <c r="K22" s="13">
+        <v>575</v>
+      </c>
+      <c r="L22" s="13">
+        <v>81</v>
+      </c>
+      <c r="M22" s="13">
+        <v>635</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
+        <v>9500</v>
+      </c>
+      <c r="B23" s="13">
+        <v>54</v>
+      </c>
+      <c r="C23" s="13">
+        <v>474</v>
+      </c>
+      <c r="D23" s="13">
+        <v>57</v>
+      </c>
+      <c r="E23" s="13">
+        <v>490</v>
+      </c>
+      <c r="F23" s="13">
+        <v>62</v>
+      </c>
+      <c r="G23" s="13">
+        <v>519</v>
+      </c>
+      <c r="H23" s="13">
+        <v>70</v>
+      </c>
+      <c r="I23" s="13">
+        <v>569</v>
+      </c>
+      <c r="J23" s="13">
+        <v>78</v>
+      </c>
+      <c r="K23" s="13">
+        <v>620</v>
+      </c>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="13">
+        <v>61</v>
+      </c>
+      <c r="C24" s="13">
+        <v>515</v>
+      </c>
+      <c r="D24" s="13">
+        <v>64</v>
+      </c>
+      <c r="E24" s="13">
+        <v>532</v>
+      </c>
+      <c r="F24" s="13">
+        <v>70</v>
+      </c>
+      <c r="G24" s="13">
+        <v>569</v>
+      </c>
+      <c r="H24" s="13">
+        <v>78</v>
+      </c>
+      <c r="I24" s="13">
+        <v>620</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>10500</v>
+      </c>
+      <c r="B25" s="13">
+        <v>71</v>
+      </c>
+      <c r="C25" s="13">
+        <v>575</v>
+      </c>
+      <c r="D25" s="13">
+        <v>75</v>
+      </c>
+      <c r="E25" s="13">
+        <v>602</v>
+      </c>
+      <c r="F25" s="13">
+        <v>81</v>
+      </c>
+      <c r="G25" s="13">
+        <v>635</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>11000</v>
+      </c>
+      <c r="B26" s="13">
+        <v>80</v>
+      </c>
+      <c r="C26" s="13">
+        <v>630</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+    </row>
+    <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+    </row>
+    <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L29" s="22"/>
+      <c r="M29" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="N29" s="24">
+        <v>62.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="R16:S16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="19" width="8.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="7">
+        <v>-50</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-40</v>
+      </c>
+      <c r="D4" s="7">
+        <v>-30</v>
+      </c>
+      <c r="E4" s="7">
+        <v>-20</v>
+      </c>
+      <c r="F4" s="7">
+        <v>-10</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>10</v>
+      </c>
+      <c r="I4" s="7">
+        <v>20</v>
+      </c>
+      <c r="J4" s="7">
+        <v>30</v>
+      </c>
+      <c r="K4" s="7">
+        <v>40</v>
+      </c>
+      <c r="L4" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <v>7000</v>
+      </c>
+      <c r="B5" s="13">
+        <v>142</v>
+      </c>
+      <c r="C5" s="13">
+        <v>142</v>
+      </c>
+      <c r="D5" s="13">
+        <v>142</v>
+      </c>
+      <c r="E5" s="13">
+        <v>142</v>
+      </c>
+      <c r="F5" s="13">
+        <v>142</v>
+      </c>
+      <c r="G5" s="13">
+        <v>142</v>
+      </c>
+      <c r="H5" s="13">
+        <v>142</v>
+      </c>
+      <c r="I5" s="13">
+        <v>141</v>
+      </c>
+      <c r="J5" s="13">
+        <v>139</v>
+      </c>
+      <c r="K5" s="13">
+        <v>137</v>
+      </c>
+      <c r="L5" s="13">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="C6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="D6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="E6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="F6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="G6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="H6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="I6" s="13">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="J6" s="13">
+        <v>136.4</v>
+      </c>
+      <c r="K6" s="13">
+        <v>135.30000000000001</v>
+      </c>
+      <c r="L6" s="13">
+        <v>134.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
+        <v>8000</v>
+      </c>
+      <c r="B7" s="13">
+        <v>131</v>
+      </c>
+      <c r="C7" s="13">
+        <v>131</v>
+      </c>
+      <c r="D7" s="13">
+        <v>131</v>
+      </c>
+      <c r="E7" s="13">
+        <v>131</v>
+      </c>
+      <c r="F7" s="13">
+        <v>131</v>
+      </c>
+      <c r="G7" s="13">
+        <v>131</v>
+      </c>
+      <c r="H7" s="13">
+        <v>131</v>
+      </c>
+      <c r="I7" s="13">
+        <v>131</v>
+      </c>
+      <c r="J7" s="13">
+        <v>131</v>
+      </c>
+      <c r="K7" s="13">
+        <v>131</v>
+      </c>
+      <c r="L7" s="13">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
+        <v>8500</v>
+      </c>
+      <c r="B8" s="13">
+        <v>120</v>
+      </c>
+      <c r="C8" s="13">
+        <v>120</v>
+      </c>
+      <c r="D8" s="13">
+        <v>120</v>
+      </c>
+      <c r="E8" s="13">
+        <v>120</v>
+      </c>
+      <c r="F8" s="13">
+        <v>120</v>
+      </c>
+      <c r="G8" s="13">
+        <v>120</v>
+      </c>
+      <c r="H8" s="13">
+        <v>120</v>
+      </c>
+      <c r="I8" s="13">
+        <v>120</v>
+      </c>
+      <c r="J8" s="13">
+        <v>120</v>
+      </c>
+      <c r="K8" s="13">
+        <v>120</v>
+      </c>
+      <c r="L8" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
+        <v>9000</v>
+      </c>
+      <c r="B9" s="13">
+        <v>112</v>
+      </c>
+      <c r="C9" s="13">
+        <v>112</v>
+      </c>
+      <c r="D9" s="13">
+        <v>112</v>
+      </c>
+      <c r="E9" s="13">
+        <v>112</v>
+      </c>
+      <c r="F9" s="13">
+        <v>112</v>
+      </c>
+      <c r="G9" s="13">
+        <v>112</v>
+      </c>
+      <c r="H9" s="13">
+        <v>112</v>
+      </c>
+      <c r="I9" s="13">
+        <v>112</v>
+      </c>
+      <c r="J9" s="13">
+        <v>112</v>
+      </c>
+      <c r="K9" s="13">
+        <v>112</v>
+      </c>
+      <c r="L9" s="13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <v>9500</v>
+      </c>
+      <c r="B10" s="13">
+        <v>90</v>
+      </c>
+      <c r="C10" s="13">
+        <v>90</v>
+      </c>
+      <c r="D10" s="13">
+        <v>90</v>
+      </c>
+      <c r="E10" s="13">
+        <v>90</v>
+      </c>
+      <c r="F10" s="13">
+        <v>90</v>
+      </c>
+      <c r="G10" s="13">
+        <v>90</v>
+      </c>
+      <c r="H10" s="13">
+        <v>90</v>
+      </c>
+      <c r="I10" s="13">
+        <v>90</v>
+      </c>
+      <c r="J10" s="13">
+        <v>90</v>
+      </c>
+      <c r="K10" s="13">
+        <v>90</v>
+      </c>
+      <c r="L10" s="13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
@@ -19943,64 +20943,62 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -20037,12 +21035,8 @@
       <c r="M17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="O17" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="N17" s="10"/>
+      <c r="O17" s="11"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="10"/>
@@ -20053,47 +21047,43 @@
         <v>7000</v>
       </c>
       <c r="B18" s="13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="13">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D18" s="13">
         <v>37</v>
       </c>
       <c r="E18" s="13">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F18" s="13">
         <v>40</v>
       </c>
       <c r="G18" s="13">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H18" s="13">
         <v>45</v>
       </c>
       <c r="I18" s="13">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J18" s="13">
         <v>51</v>
       </c>
       <c r="K18" s="13">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L18" s="13">
         <v>60</v>
       </c>
       <c r="M18" s="13">
-        <v>511</v>
-      </c>
-      <c r="N18" s="13">
-        <v>72</v>
-      </c>
-      <c r="O18" s="13">
-        <v>580</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
@@ -20104,47 +21094,43 @@
         <v>7500</v>
       </c>
       <c r="B19" s="13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="13">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D19" s="13">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" s="13">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="F19" s="13">
         <v>43</v>
       </c>
       <c r="G19" s="13">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="H19" s="13">
         <v>48</v>
       </c>
       <c r="I19" s="13">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="J19" s="13">
         <v>55</v>
       </c>
       <c r="K19" s="13">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="L19" s="13">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M19" s="13">
-        <v>532</v>
-      </c>
-      <c r="N19" s="13">
-        <v>76</v>
-      </c>
-      <c r="O19" s="13">
-        <v>605</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
@@ -20155,40 +21141,40 @@
         <v>8000</v>
       </c>
       <c r="B20" s="13">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="13">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D20" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="13">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="F20" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" s="13">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="H20" s="13">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I20" s="13">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="J20" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K20" s="13">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="L20" s="13">
         <v>69</v>
       </c>
       <c r="M20" s="13">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
@@ -20202,40 +21188,40 @@
         <v>8500</v>
       </c>
       <c r="B21" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="13">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="D21" s="13">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E21" s="13">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F21" s="13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G21" s="13">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="H21" s="13">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I21" s="13">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="J21" s="13">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K21" s="13">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="L21" s="13">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M21" s="13">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
@@ -20249,34 +21235,34 @@
         <v>9000</v>
       </c>
       <c r="B22" s="13">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22" s="13">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D22" s="13">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E22" s="13">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="F22" s="13">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G22" s="13">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="H22" s="13">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I22" s="13">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="J22" s="13">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K22" s="13">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
@@ -20292,28 +21278,28 @@
         <v>9500</v>
       </c>
       <c r="B23" s="13">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C23" s="13">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="D23" s="13">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E23" s="13">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="F23" s="13">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G23" s="13">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="H23" s="13">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I23" s="13">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
@@ -20331,22 +21317,22 @@
         <v>10000</v>
       </c>
       <c r="B24" s="13">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C24" s="13">
-        <v>515</v>
+        <v>555</v>
       </c>
       <c r="D24" s="13">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E24" s="13">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="F24" s="13">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G24" s="13">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
@@ -20365,18 +21351,10 @@
       <c r="A25" s="8">
         <v>10500</v>
       </c>
-      <c r="B25" s="13">
-        <v>71</v>
-      </c>
-      <c r="C25" s="13">
-        <v>575</v>
-      </c>
-      <c r="D25" s="13">
-        <v>75</v>
-      </c>
-      <c r="E25" s="13">
-        <v>602</v>
-      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
@@ -20416,27 +21394,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -20444,11 +21422,18 @@
         <v>99</v>
       </c>
       <c r="N29" s="24">
-        <v>62.5</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -20456,833 +21441,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:S29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="19" width="8.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="7">
-        <v>-50</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-40</v>
-      </c>
-      <c r="D4" s="7">
-        <v>-30</v>
-      </c>
-      <c r="E4" s="7">
-        <v>-20</v>
-      </c>
-      <c r="F4" s="7">
-        <v>-10</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>10</v>
-      </c>
-      <c r="I4" s="7">
-        <v>20</v>
-      </c>
-      <c r="J4" s="7">
-        <v>30</v>
-      </c>
-      <c r="K4" s="7">
-        <v>40</v>
-      </c>
-      <c r="L4" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
-        <v>7000</v>
-      </c>
-      <c r="B5" s="13">
-        <v>142</v>
-      </c>
-      <c r="C5" s="13">
-        <v>142</v>
-      </c>
-      <c r="D5" s="13">
-        <v>142</v>
-      </c>
-      <c r="E5" s="13">
-        <v>142</v>
-      </c>
-      <c r="F5" s="13">
-        <v>142</v>
-      </c>
-      <c r="G5" s="13">
-        <v>142</v>
-      </c>
-      <c r="H5" s="13">
-        <v>142</v>
-      </c>
-      <c r="I5" s="13">
-        <v>141</v>
-      </c>
-      <c r="J5" s="13">
-        <v>139</v>
-      </c>
-      <c r="K5" s="13">
-        <v>137</v>
-      </c>
-      <c r="L5" s="13">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
-        <v>7500</v>
-      </c>
-      <c r="B6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="C6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="D6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="E6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="F6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="G6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="H6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="I6" s="13">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="J6" s="13">
-        <v>136.4</v>
-      </c>
-      <c r="K6" s="13">
-        <v>135.30000000000001</v>
-      </c>
-      <c r="L6" s="13">
-        <v>134.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
-        <v>8000</v>
-      </c>
-      <c r="B7" s="13">
-        <v>131</v>
-      </c>
-      <c r="C7" s="13">
-        <v>131</v>
-      </c>
-      <c r="D7" s="13">
-        <v>131</v>
-      </c>
-      <c r="E7" s="13">
-        <v>131</v>
-      </c>
-      <c r="F7" s="13">
-        <v>131</v>
-      </c>
-      <c r="G7" s="13">
-        <v>131</v>
-      </c>
-      <c r="H7" s="13">
-        <v>131</v>
-      </c>
-      <c r="I7" s="13">
-        <v>131</v>
-      </c>
-      <c r="J7" s="13">
-        <v>131</v>
-      </c>
-      <c r="K7" s="13">
-        <v>131</v>
-      </c>
-      <c r="L7" s="13">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
-        <v>8500</v>
-      </c>
-      <c r="B8" s="13">
-        <v>120</v>
-      </c>
-      <c r="C8" s="13">
-        <v>120</v>
-      </c>
-      <c r="D8" s="13">
-        <v>120</v>
-      </c>
-      <c r="E8" s="13">
-        <v>120</v>
-      </c>
-      <c r="F8" s="13">
-        <v>120</v>
-      </c>
-      <c r="G8" s="13">
-        <v>120</v>
-      </c>
-      <c r="H8" s="13">
-        <v>120</v>
-      </c>
-      <c r="I8" s="13">
-        <v>120</v>
-      </c>
-      <c r="J8" s="13">
-        <v>120</v>
-      </c>
-      <c r="K8" s="13">
-        <v>120</v>
-      </c>
-      <c r="L8" s="13">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
-        <v>9000</v>
-      </c>
-      <c r="B9" s="13">
-        <v>112</v>
-      </c>
-      <c r="C9" s="13">
-        <v>112</v>
-      </c>
-      <c r="D9" s="13">
-        <v>112</v>
-      </c>
-      <c r="E9" s="13">
-        <v>112</v>
-      </c>
-      <c r="F9" s="13">
-        <v>112</v>
-      </c>
-      <c r="G9" s="13">
-        <v>112</v>
-      </c>
-      <c r="H9" s="13">
-        <v>112</v>
-      </c>
-      <c r="I9" s="13">
-        <v>112</v>
-      </c>
-      <c r="J9" s="13">
-        <v>112</v>
-      </c>
-      <c r="K9" s="13">
-        <v>112</v>
-      </c>
-      <c r="L9" s="13">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
-        <v>9500</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
-        <v>10000</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
-        <v>10500</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
-        <v>11000</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
-      <c r="B17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="11"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
-        <v>7000</v>
-      </c>
-      <c r="B18" s="13">
-        <v>35</v>
-      </c>
-      <c r="C18" s="13">
-        <v>382</v>
-      </c>
-      <c r="D18" s="13">
-        <v>37</v>
-      </c>
-      <c r="E18" s="13">
-        <v>394</v>
-      </c>
-      <c r="F18" s="13">
-        <v>40</v>
-      </c>
-      <c r="G18" s="13">
-        <v>410</v>
-      </c>
-      <c r="H18" s="13">
-        <v>45</v>
-      </c>
-      <c r="I18" s="13">
-        <v>435</v>
-      </c>
-      <c r="J18" s="13">
-        <v>51</v>
-      </c>
-      <c r="K18" s="13">
-        <v>465</v>
-      </c>
-      <c r="L18" s="13">
-        <v>55</v>
-      </c>
-      <c r="M18" s="13">
-        <v>488</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
-        <v>7500</v>
-      </c>
-      <c r="B19" s="13">
-        <v>38</v>
-      </c>
-      <c r="C19" s="13">
-        <v>399</v>
-      </c>
-      <c r="D19" s="13">
-        <v>40</v>
-      </c>
-      <c r="E19" s="13">
-        <v>410</v>
-      </c>
-      <c r="F19" s="13">
-        <v>43</v>
-      </c>
-      <c r="G19" s="13">
-        <v>425</v>
-      </c>
-      <c r="H19" s="13">
-        <v>48</v>
-      </c>
-      <c r="I19" s="13">
-        <v>455</v>
-      </c>
-      <c r="J19" s="13">
-        <v>55</v>
-      </c>
-      <c r="K19" s="13">
-        <v>485</v>
-      </c>
-      <c r="L19" s="13">
-        <v>60</v>
-      </c>
-      <c r="M19" s="13">
-        <v>515</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
-        <v>8000</v>
-      </c>
-      <c r="B20" s="13">
-        <v>41</v>
-      </c>
-      <c r="C20" s="13">
-        <v>416</v>
-      </c>
-      <c r="D20" s="13">
-        <v>43</v>
-      </c>
-      <c r="E20" s="13">
-        <v>428</v>
-      </c>
-      <c r="F20" s="13">
-        <v>47</v>
-      </c>
-      <c r="G20" s="13">
-        <v>446</v>
-      </c>
-      <c r="H20" s="13">
-        <v>53</v>
-      </c>
-      <c r="I20" s="13">
-        <v>474</v>
-      </c>
-      <c r="J20" s="13">
-        <v>60</v>
-      </c>
-      <c r="K20" s="13">
-        <v>515</v>
-      </c>
-      <c r="L20" s="13">
-        <v>64</v>
-      </c>
-      <c r="M20" s="13">
-        <v>538</v>
-      </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
-        <v>8500</v>
-      </c>
-      <c r="B21" s="13">
-        <v>45</v>
-      </c>
-      <c r="C21" s="13">
-        <v>438</v>
-      </c>
-      <c r="D21" s="13">
-        <v>48</v>
-      </c>
-      <c r="E21" s="13">
-        <v>452</v>
-      </c>
-      <c r="F21" s="13">
-        <v>52</v>
-      </c>
-      <c r="G21" s="13">
-        <v>472</v>
-      </c>
-      <c r="H21" s="13">
-        <v>58</v>
-      </c>
-      <c r="I21" s="13">
-        <v>502</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
-        <v>9000</v>
-      </c>
-      <c r="B22" s="13">
-        <v>51</v>
-      </c>
-      <c r="C22" s="13">
-        <v>466</v>
-      </c>
-      <c r="D22" s="13">
-        <v>54</v>
-      </c>
-      <c r="E22" s="13">
-        <v>480</v>
-      </c>
-      <c r="F22" s="13">
-        <v>59</v>
-      </c>
-      <c r="G22" s="13">
-        <v>508</v>
-      </c>
-      <c r="H22" s="13">
-        <v>66</v>
-      </c>
-      <c r="I22" s="13">
-        <v>548</v>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
-        <v>9500</v>
-      </c>
-      <c r="B23" s="13">
-        <v>58</v>
-      </c>
-      <c r="C23" s="13">
-        <v>501</v>
-      </c>
-      <c r="D23" s="13">
-        <v>61</v>
-      </c>
-      <c r="E23" s="13">
-        <v>518</v>
-      </c>
-      <c r="F23" s="13">
-        <v>67</v>
-      </c>
-      <c r="G23" s="13">
-        <v>555</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
-        <v>10000</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
-        <v>10500</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>11000</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
-    </row>
-    <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-    </row>
-    <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L29" s="22"/>
-      <c r="M29" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="N29" s="24">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21691,64 +21849,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -22236,27 +22394,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -22297,43 +22455,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -22719,64 +22877,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -23272,27 +23430,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -23305,6 +23463,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -23312,13 +23477,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23335,43 +23493,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -23757,64 +23915,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -24314,27 +24472,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -24347,6 +24505,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -24354,13 +24519,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24376,43 +24534,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -24798,66 +24956,66 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31" t="s">
+      <c r="O16" s="36"/>
+      <c r="P16" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -25381,27 +25539,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -25414,6 +25572,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -25421,13 +25586,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25444,43 +25602,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -25866,64 +26024,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -26411,27 +26569,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -26444,6 +26602,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A3:L3"/>
@@ -26451,13 +26616,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="N16:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26865,64 +27023,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -27422,27 +27580,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
@@ -27875,64 +28033,64 @@
       <c r="A15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="36"/>
+      <c r="H16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="31" t="s">
+      <c r="K16" s="36"/>
+      <c r="L16" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="31" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
@@ -28416,27 +28574,27 @@
       <c r="S26" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L29" s="22"/>
